--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-cleaning-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-cleaning-hard.xlsx
@@ -463,13 +463,13 @@
         <v>Lọc bỏ các Outliers cực trị dựa trên ngưỡng vật lý (nhiệt độ phòng không thể vượt quá 100 độ C), thay thế Outliers và các giá trị NULL bằng phương pháp nội suy tuyến tính (Linear Interpolation) dựa trên các giây liền kề — lọc vật lý và nội suy chuỗi thời gian</v>
       </c>
       <c r="G2" t="str">
+        <v>Điền giá trị trung bình (mean) của toàn bộ nhiệt độ đo được trong một tháng vào tất cả các ô bị trống và ô Outlier — điền trung bình tháng làm mất đặc trưng cục bộ</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Giữ nguyên bộ dữ liệu thô vì mô hình dự báo AI sẽ tự động học cách bỏ qua các giá trị nhiễu này — chủ quan không xử lý nhiễu</v>
+      </c>
+      <c r="I2" t="str">
         <v>Xóa bỏ toàn bộ các dòng chứa dữ liệu khuyết thiếu và Outliers khỏi bộ dữ liệu — xóa bỏ bản ghi thô làm mất tính liên tục thời gian</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Điền giá trị trung bình (mean) của toàn bộ nhiệt độ đo được trong một tháng vào tất cả các ô bị trống và ô Outlier — điền trung bình tháng làm mất đặc trưng cục bộ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Giữ nguyên bộ dữ liệu thô vì mô hình dự báo AI sẽ tự động học cách bỏ qua các giá trị nhiễu này — chủ quan không xử lý nhiễu</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -495,13 +495,13 @@
         <v>Chuyển về chữ thường, loại bỏ ký tự đặc biệt/dấu câu, tách từ tiếng Việt (Word Segmentation), loại bỏ các từ dừng (Stopwords tiếng Việt như "và", "hoặc", "thì") — quy trình tiền xử lý văn bản NLP</v>
       </c>
       <c r="G3" t="str">
-        <v>Dịch toàn bộ văn bản sang tiếng Anh bằng API dịch máy, sau đó ép kiểu dữ liệu sang dạng số nguyên — dịch thuật ép kiểu</v>
+        <v>Mã hóa toàn bộ văn bản thành các chuỗi số nhị phân MD5 để bảo mật thông tin khách hàng — mã hóa MD5</v>
       </c>
       <c r="H3" t="str">
         <v>Xóa bỏ toàn bộ các câu văn có độ dài trên 20 từ để tiết kiệm bộ nhớ RAM khi chạy thuật toán — cắt ngắn văn bản cưỡng bức</v>
       </c>
       <c r="I3" t="str">
-        <v>Mã hóa toàn bộ văn bản thành các chuỗi số nhị phân MD5 để bảo mật thông tin khách hàng — mã hóa MD5</v>
+        <v>Dịch toàn bộ văn bản sang tiếng Anh bằng API dịch máy, sau đó ép kiểu dữ liệu sang dạng số nguyên — dịch thuật ép kiểu</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>Dữ liệu quá lệch sẽ làm mô hình luôn dự báo là "Bình thường" vì độ chính xác vẫn đạt 99.5% nhưng vô dụng vì bỏ sót 100% ca lừa đảo. SMOTE (Synthetic Minority Over-sampling Technique) sinh thêm dữ liệu giả lập dựa trên khoảng cách K-Nearest Neighbors của các mẫu thiểu số thực tế. Bắt buộc phải chia train/test trước khi chạy SMOTE để tránh việc dữ liệu kiểm thử bị rò rỉ vào tập huấn luyện.</v>
       </c>
       <c r="F4" t="str">
-        <v>Áp dụng kỹ thuật lấy mẫu lại (Resampling) bằng cách tăng mẫu thiểu số (Oversampling với thuật toán SMOTE) hoặc giảm mẫu đa số (Undersampling), kết hợp chia tập train/test trước khi xử lý để tránh rò rỉ dữ liệu (Data Leakage) — xử lý mất cân bằng dữ liệu khoa học</v>
+        <v>Sao chép thủ công các dòng dữ liệu lừa đảo lặp đi lặp lại nhiều lần trong file Excel cho đến khi số lượng bằng nhau — sao chép thủ công lặp lại</v>
       </c>
       <c r="G4" t="str">
-        <v>Sao chép thủ công các dòng dữ liệu lừa đảo lặp đi lặp lại nhiều lần trong file Excel cho đến khi số lượng bằng nhau — sao chép thủ công lặp lại</v>
+        <v>Giữ nguyên dữ liệu thô và yêu cầu mô hình AI tự điều chỉnh các tham số trọng số mà không cần xử lý dữ liệu đầu vào — đùn đẩy cho mô hình</v>
       </c>
       <c r="H4" t="str">
         <v>Xóa bớt dữ liệu hồ sơ bình thường đi cho đến khi số lượng bằng đúng số lượng hồ sơ lừa đảo (chỉ giữ lại 0.5% dữ liệu gốc) — undersampling cực đoan mất thông tin</v>
       </c>
       <c r="I4" t="str">
-        <v>Giữ nguyên dữ liệu thô và yêu cầu mô hình AI tự điều chỉnh các tham số trọng số mà không cần xử lý dữ liệu đầu vào — đùn đẩy cho mô hình</v>
+        <v>Áp dụng kỹ thuật lấy mẫu lại (Resampling) bằng cách tăng mẫu thiểu số (Oversampling với thuật toán SMOTE) hoặc giảm mẫu đa số (Undersampling), kết hợp chia tập train/test trước khi xử lý để tránh rò rỉ dữ liệu (Data Leakage) — xử lý mất cân bằng dữ liệu khoa học</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>MAR (Khuyết ngẫu nhiên) xảy ra khi xác suất khuyết của biến Y phụ thuộc vào một biến khác X đã quan sát được (ở đây, việc khuyết Cân nặng phụ thuộc vào Tuổi và Giới tính). Vì thế, dùng MICE/Hồi quy dựa trên X để dự báo Y sẽ cho kết quả điền khuyết có độ tin cậy cao nhất, tránh thiên lệch hệ thống.</v>
       </c>
       <c r="F5" t="str">
+        <v>Đây là lỗi hệ thống nhập liệu phần mềm; giải pháp là khóa tài khoản của các bác sĩ đã nhập liệu thiếu thông tin bệnh nhân — kỷ luật nhân sự</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Missing Not at Random (MNAR) vì việc thiếu dữ liệu hoàn toàn không liên quan gì đến các biến khác; giải pháp là điền số 0 vào tất cả các ô bị trống — điền số 0 phá vỡ phân phối</v>
+      </c>
+      <c r="H5" t="str">
         <v>Missing at Random (MAR) vì xác suất khuyết phụ thuộc vào biến quan sát được là Giới tính và Độ tuổi; giải pháp tối ưu là điền khuyết bằng mô hình hồi quy đa biến (như MICE) sử dụng thông tin tuổi và giới tính để dự báo — MAR điền khuyết đa biến</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Missing Completely at Random (MCAR) vì việc khuyết thiếu hoàn toàn ngẫu nhiên không theo quy luật nào; giải pháp là xóa bỏ hoàn toàn các dòng bị thiếu — xóa dòng khuyết sai cơ chế</v>
       </c>
-      <c r="H5" t="str">
-        <v>Missing Not at Random (MNAR) vì việc thiếu dữ liệu hoàn toàn không liên quan gì đến các biến khác; giải pháp là điền số 0 vào tất cả các ô bị trống — điền số 0 phá vỡ phân phối</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Đây là lỗi hệ thống nhập liệu phần mềm; giải pháp là khóa tài khoản của các bác sĩ đã nhập liệu thiếu thông tin bệnh nhân — kỷ luật nhân sự</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -591,10 +591,10 @@
         <v>Xảy ra khi các thông tin của tập kiểm thử (Test set) vô tình được đưa vào để tính toán các tham số tiền xử lý (như tính Mean để fillna hoặc Min/Max để Scaling) của tập huấn luyện (Train set); phòng tránh bằng cách chia tập Train/Test trước và chỉ chạy hàm `.fit_transform()` trên tập Train, sau đó áp dụng `.transform()` lên tập Test — ngăn chặn rò rỉ thông tin tập test</v>
       </c>
       <c r="G6" t="str">
+        <v>Xảy ra khi lập trình viên quên không lưu tệp tin code sau khi hoàn thành công việc dọn dẹp dữ liệu — mất mát mã nguồn</v>
+      </c>
+      <c r="H6" t="str">
         <v>Xảy ra khi cơ sở dữ liệu của dự án bị hacker tấn công và lấy trộm thông tin khách hàng ra ngoài; phòng tránh bằng cách cài đặt tường lửa — bảo mật an ninh mạng</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Xảy ra khi lập trình viên quên không lưu tệp tin code sau khi hoàn thành công việc dọn dẹp dữ liệu — mất mát mã nguồn</v>
       </c>
       <c r="I6" t="str">
         <v>Xảy ra khi dữ liệu số bị tràn bộ nhớ do kiểu dữ liệu khai báo quá nhỏ so với giá trị thực tế — tràn bộ nhớ dữ liệu</v>
@@ -620,19 +620,19 @@
         <v>Mã bưu chính, mã tỉnh thành (ví dụ mã tỉnh `01`), số điện thoại không phải là số để tính toán mà là mã định danh dạng chuỗi (Text). Nếu lưu kiểu Numeric (int), các chữ số 0 ở đầu (Leading zeros) sẽ tự động bị lược bỏ. Cần ép kiểu String và dùng zfill (zero fill)/LPAD để khôi phục cấu trúc chuẩn.</v>
       </c>
       <c r="F7" t="str">
+        <v>Yêu cầu khách hàng tự viết đơn giải trình lý do tại sao mã bưu chính của họ lại thiếu chữ số 0 — yêu cầu khách hàng giải trình</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Tự động cộng thêm 90000 vào tất cả các giá trị mã bưu chính nhỏ hơn 100000 để đưa chúng về độ dài 6 chữ số — cộng hằng số sai lệch logic</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Xóa bỏ toàn bộ các mã bưu chính bị thiếu số 0 ở đầu vì đây là dữ liệu lỗi không thể phục hồi — xóa bỏ dữ liệu lỗi đầu số</v>
+      </c>
+      <c r="I7" t="str">
         <v>Ép kiểu dữ liệu cột sang dạng chuỗi ký tự (String/Text), sau đó sử dụng hàm chèn đệm (như `.str.zfill(6)` trong Python hoặc LPAD trong SQL) để tự động thêm chữ số 0 vào đầu cho đủ độ dài quy định — hàm chèn đệm LPAD/zfill</v>
       </c>
-      <c r="G7" t="str">
-        <v>Xóa bỏ toàn bộ các mã bưu chính bị thiếu số 0 ở đầu vì đây là dữ liệu lỗi không thể phục hồi — xóa bỏ dữ liệu lỗi đầu số</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Tự động cộng thêm 90000 vào tất cả các giá trị mã bưu chính nhỏ hơn 100000 để đưa chúng về độ dài 6 chữ số — cộng hằng số sai lệch logic</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Yêu cầu khách hàng tự viết đơn giải trình lý do tại sao mã bưu chính của họ lại thiếu chữ số 0 — yêu cầu khách hàng giải trình</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Trong phân tích cảm xúc (Sentiment Analysis), emoji mang thông điệp rất mạnh mẽ (thậm chí mạnh hơn chữ viết). Việc chuyển đổi emoji sang text tương đương (Emoji-to-text mapping) giúp giữ lại các sắc thái cảm xúc quan trọng cho thuật toán xử lý ngôn ngữ tự nhiên.</v>
       </c>
       <c r="F8" t="str">
-        <v>Chuyển đổi các emoji phổ biến thành các từ mang ý nghĩa tương ứng (ví dụ: 😊 thành "vui/hài lòng", 😢 thành "buồn/thất vọng") để mô hình NLP đọc hiểu được, hoặc loại bỏ hoàn toàn các emoji không có ý nghĩa phân tích — chuẩn hóa chuyển đổi emoji</v>
+        <v>Xóa bỏ toàn bộ bài viết nếu bài viết đó có chứa bất kỳ ký tự emoji nào — xóa bỏ bài viết chứa emoji</v>
       </c>
       <c r="G8" t="str">
-        <v>Xóa bỏ toàn bộ bài viết nếu bài viết đó có chứa bất kỳ ký tự emoji nào — xóa bỏ bài viết chứa emoji</v>
+        <v>Yêu cầu khách hàng không được phép sử dụng các biểu tượng cảm xúc khi viết đánh giá trên ứng dụng di động — hạn chế người dùng</v>
       </c>
       <c r="H8" t="str">
         <v>Giữ nguyên emoji và ép kiểu dữ liệu của cột review sang dạng số thực float — ép kiểu float sai lệch</v>
       </c>
       <c r="I8" t="str">
-        <v>Yêu cầu khách hàng không được phép sử dụng các biểu tượng cảm xúc khi viết đánh giá trên ứng dụng di động — hạn chế người dùng</v>
+        <v>Chuyển đổi các emoji phổ biến thành các từ mang ý nghĩa tương ứng (ví dụ: 😊 thành "vui/hài lòng", 😢 thành "buồn/thất vọng") để mô hình NLP đọc hiểu được, hoặc loại bỏ hoàn toàn các emoji không có ý nghĩa phân tích — chuẩn hóa chuyển đổi emoji</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Khi hai biến tương quan quá mạnh (ví dụ: Chiều cao và Chiều dài chân), mô hình hồi quy tuyến tính không thể phân biệt được biến nào thực sự tác động đến kết quả. DA phải kiểm tra hệ số VIF (Variance Inflation Factor), nếu VIF &gt; 5-10 thì cần loại bỏ bớt một trong các biến tương quan mạnh đó.</v>
       </c>
       <c r="F9" t="str">
+        <v>Vì đa cộng tuyến tự động làm tăng dung lượng lưu trữ của tệp tin database lên gấp 10 lần — tăng bộ nhớ lưu trữ</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Vì đa cộng tuyến làm sập máy chủ chạy thuật toán do tràn bộ nhớ RAM của vi xử lý — tràn bộ nhớ RAM</v>
+      </c>
+      <c r="H9" t="str">
         <v>Vì đa cộng tuyến làm mất tính ổn định của các hệ số hồi quy (coefficients), khiến mô hình khó xác định chính xác mức độ tác động riêng biệt của từng biến lên biến mục tiêu — mất tính ổn định hệ số</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Vì đa cộng tuyến tự động làm tăng dung lượng lưu trữ của tệp tin database lên gấp 10 lần — tăng bộ nhớ lưu trữ</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Vì đa cộng tuyến làm sập máy chủ chạy thuật toán do tràn bộ nhớ RAM của vi xử lý — tràn bộ nhớ RAM</v>
       </c>
       <c r="I9" t="str">
         <v>Vì đa cộng tuyến là yêu cầu bảo mật thông tin bắt buộc đối với các dự án y tế và tài chính — bảo mật thông tin</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Giá âm trong dữ liệu bán hàng thường đại diện cho các nghiệp vụ trả hàng (Refund) hoặc giảm giá. Việc tự ý đổi thành số dương (bằng hàm trị tuyệt đối) hoặc xóa đi sẽ làm sai lệch hoàn toàn dòng tiền thực tế và báo cáo doanh thu thuần (Net Revenue).</v>
       </c>
       <c r="F10" t="str">
+        <v>Thay thế toàn bộ các mức giá âm bằng giá trung bình của các sản phẩm cùng loại trong kho — điền giá trị trung bình sai lệch</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Xóa bỏ ngay lập tức tất cả các dòng giao dịch có giá âm ra khỏi cơ sở dữ liệu để báo cáo doanh thu luôn đạt số dương — xóa bỏ bản ghi thô làm sai lệch dòng tiền</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Tự động chạy hàm trị tuyệt đối ABS() để biến đổi toàn bộ các mức giá âm thành giá dương cho đồng bộ — sửa đổi cơ học sai lệch bản chất</v>
+      </c>
+      <c r="I10" t="str">
         <v>Đối chiếu mã loại giao dịch (Transaction Type): Nếu là giao dịch hoàn tiền (Refund/Return) hoặc mã giảm giá (Discount) thì giá âm là hợp lệ; nếu là giao dịch bán thường thì đây là lỗi nhập liệu, cần xử lý theo quy tắc nghiệp vụ — phân tích nghiệp vụ theo loại giao dịch</v>
       </c>
-      <c r="G10" t="str">
-        <v>Tự động chạy hàm trị tuyệt đối ABS() để biến đổi toàn bộ các mức giá âm thành giá dương cho đồng bộ — sửa đổi cơ học sai lệch bản chất</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Xóa bỏ ngay lập tức tất cả các dòng giao dịch có giá âm ra khỏi cơ sở dữ liệu để báo cáo doanh thu luôn đạt số dương — xóa bỏ bản ghi thô làm sai lệch dòng tiền</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Thay thế toàn bộ các mức giá âm bằng giá trung bình của các sản phẩm cùng loại trong kho — điền giá trị trung bình sai lệch</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Trong tính toán phân tán, dữ liệu được chia nhỏ (partitions) lưu trên nhiều máy (nodes). Loại bỏ trùng lặp (drop_duplicates) yêu cầu các máy phải truyền dữ liệu qua lại cho nhau (Shuffle) để so sánh xem có trùng không, đây là tác vụ tốn kém tài nguyên nhất. Cần tối ưu bằng cách gom nhóm dữ liệu (map-side aggregation) hoặc lọc sớm từ nguồn.</v>
       </c>
       <c r="F11" t="str">
+        <v>Vì Spark chỉ hỗ trợ nạp dữ liệu thô vào bộ nhớ RAM chứ không cho phép thực hiện bất kỳ phép lọc nào — giới hạn tính năng Spark</v>
+      </c>
+      <c r="G11" t="str">
         <v>Vì các hàm này yêu cầu xáo trộn dữ liệu (Data Shuffling) giữa các nodes trong mạng để đối chiếu dữ liệu trùng lặp, gây nghẽn băng thông mạng cực lớn — tắc nghẽn băng thông do Data Shuffling</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
+        <v>Vì các hàm này bắt buộc Spark phải dịch chuyển dữ liệu về chạy trên một máy tính cá nhân duy nhất của lập trình viên — chạy đơn luồng</v>
+      </c>
+      <c r="I11" t="str">
         <v>Vì Spark sẽ tự động khóa toàn bộ ổ cứng của các nodes nếu phát hiện có dòng dữ liệu bị khuyết thiếu — khóa ổ cứng nodes</v>
       </c>
-      <c r="H11" t="str">
-        <v>Vì Spark chỉ hỗ trợ nạp dữ liệu thô vào bộ nhớ RAM chứ không cho phép thực hiện bất kỳ phép lọc nào — giới hạn tính năng Spark</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Vì các hàm này bắt buộc Spark phải dịch chuyển dữ liệu về chạy trên một máy tính cá nhân duy nhất của lập trình viên — chạy đơn luồng</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
